--- a/data/google_news_dedup_audit_02_0426_UTC.xlsx
+++ b/data/google_news_dedup_audit_02_0426_UTC.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,17 +445,17 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2" t="n">
         <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7852948904037476</v>
+        <v>0.7708263397216797</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Postcodes in Wales hit by Royal Mail delivery disruption today — full list - walesonline.co.uk</t>
+          <t>Postcodes in Wales hit by Royal Mail delivery disruption today — full list - Wales Online</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -466,17 +466,17 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B3" t="n">
         <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7674502730369568</v>
+        <v>0.7487115859985352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Postcodes in Wales hit by Royal Mail delivery disruption today — full list - walesonline.co.uk</t>
+          <t>Postcodes in Wales hit by Royal Mail delivery disruption today — full list - Wales Online</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -487,190 +487,22 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="B4" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6804190874099731</v>
+        <v>0.7581480741500854</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Postcodes in Wales hit by Royal Mail delivery disruption today — full list - walesonline.co.uk</t>
+          <t>Woman stabbed to death after letting man into her home in Croydon - london-now.co.uk</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Royal Mail delivery alert as 28 postcodes face delays — full list - Daily Express</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>11</v>
-      </c>
-      <c r="B5" t="n">
-        <v>12</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.6862471699714661</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>DHL Supply Chain Expands Airport Role With Air France-KLM - Supply Chain Digital Magazine</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Air France selects DHL Supply Chain to deliver ground handling services at London Gatwick - Passenger Terminal Today</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B6" t="n">
-        <v>13</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.7231398224830627</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>DHL Supply Chain Expands Airport Role With Air France-KLM - Supply Chain Digital Magazine</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>DHL Supply Chain appointed by Air France - Freightweek</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>17</v>
-      </c>
-      <c r="B7" t="n">
-        <v>18</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.5452268123626709</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Man krijgt kogel in de arm bij schietpartij vlak bij metrostation Clemenceau in Anderlecht - VRT</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Schietpartij Anderlecht: slachtoffer kreeg kogel in arm - GVA</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>17</v>
-      </c>
-      <c r="B8" t="n">
-        <v>19</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.5183743238449097</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Man krijgt kogel in de arm bij schietpartij vlak bij metrostation Clemenceau in Anderlecht - VRT</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Schietpartij Anderlecht: slachtoffer kreeg kogel in arm - Nieuwsblad</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>17</v>
-      </c>
-      <c r="B9" t="n">
-        <v>24</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.7620973587036133</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Man krijgt kogel in de arm bij schietpartij vlak bij metrostation Clemenceau in Anderlecht - VRT</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Man krijgt kogel in arm na zoveelste schietpartij in Anderlecht - v-nieuws.be</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>76</v>
-      </c>
-      <c r="B10" t="n">
-        <v>77</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.8777137398719788</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Attentat déjoué contre Bank of America : quatre jeunes écroués à Paris - France 24</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Attentat déjoué contre la Bank of America à Paris : trois mineurs et un majeur, suspecté de les avoir recrutés, mis en examen - France Info</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>76</v>
-      </c>
-      <c r="B11" t="n">
-        <v>78</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.9249871969223022</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Attentat déjoué contre Bank of America : quatre jeunes écroués à Paris - France 24</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Attentat déjoué contre Bank of America à Paris : où en est l'enquête ? - TF1 Info</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>76</v>
-      </c>
-      <c r="B12" t="n">
-        <v>80</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.7324134707450867</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Attentat déjoué contre Bank of America : quatre jeunes écroués à Paris - France 24</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Tentative d’attentat à Paris contre Bank of America: la justice explore la piste pro-iranienne - RFI</t>
+          <t>Shock after ‘lovely’ elderly woman stabbed to death outside her home - london-now.co.uk</t>
         </is>
       </c>
     </row>
